--- a/artfynd/A 19977-2021 artfynd.xlsx
+++ b/artfynd/A 19977-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19977-2021 artfynd.xlsx
+++ b/artfynd/A 19977-2021 artfynd.xlsx
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
